--- a/8_ipscore_rebuild/4_tool/ipscore_valuation_data.xlsx
+++ b/8_ipscore_rebuild/4_tool/ipscore_valuation_data.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,149 +441,183 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rapid point-of-care test for antibiotic resistance markers</t>
+          <t>Method for detecting and characterising a microorganism</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Plain_Title</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>worked example - stands in for a family from module 6's corpus (V5)</t>
+          <t>Rapid identification and antibiotic-susceptibility testing of bacteria</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Applicant</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a mid-size European diagnostics company</t>
+          <t>EP3074539B1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>in-vitro diagnostics / antimicrobial resistance</t>
-        </is>
+          <t>Docdb_Family_Id</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>53398085</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Business turnover</t>
+          <t>Applicant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1,500,000 EUR</t>
+          <t>Q-Linea AB, Uppsala (SE)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Direct costs</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>900,000 EUR</t>
+          <t>in-vitro diagnostics / antimicrobial resistance</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Indirect costs</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>225,000 EUR</t>
+          <t>real family, picked from module 6's corpus on TIP 2026-08-15 (decision V5)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Business turnover</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>45,000 EUR</t>
+          <t>1,500,000 EUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Depreciation period</t>
+          <t>Direct costs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>900,000 EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of turnover in this business area</t>
+          <t>Indirect costs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>225,000 EUR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Discount rate</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>45,000 EUR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>-&gt; cost share (derived)</t>
+          <t>Depreciation period</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>75% of turnover</t>
+          <t>7 years</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Share of turnover in this business area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Discount rate</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>-&gt; cost share (derived)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>75% of turnover</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>-&gt; investment index (derived)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
@@ -726,7 +760,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (strong): granted flag + publication kind codes across the family</t>
+          <t>-&gt; notebook 2 (strong): tls201_appln.granted ('Y'/'N') + publication kind codes, plus the opposition outcome from tls231 (26N none / 26 filed / 27W revoked)</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -747,7 +781,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>granted flag + publication kind codes across the family</t>
+          <t>tls201_appln.granted ('Y'/'N') + publication kind codes, plus the opposition outcome from tls231 (26N none / 26 filed / 27W revoked)</t>
         </is>
       </c>
     </row>
@@ -846,7 +880,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (strong): earliest filing date + 20 years -&gt; nominal remaining term (an upper bound; actual lapses need legal-status data)</t>
+          <t>-&gt; notebook 2 (strong): earliest filing date + 20 years for the nominal term, and tls231 PGFP renewal payments (fee_renewal_year) for how far fees are actually paid</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -867,7 +901,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>earliest filing date + 20 years -&gt; nominal remaining term (an upper bound; actual lapses need legal-status data)</t>
+          <t>earliest filing date + 20 years for the nominal term, and tls231 PGFP renewal payments (fee_renewal_year) for how far fees are actually paid</t>
         </is>
       </c>
     </row>
@@ -912,7 +946,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (proxy): claim count and IPC breadth - breadth is not count, label it</t>
+          <t>-&gt; notebook 2 (proxy): tls211_pat_publn.publn_claims - take it from the B1 (100% covered, mean 11.5 for granted EP), never the A1 (51%, and those are the as-filed claims). WO has 0% coverage. Breadth is not count, so label it</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -933,7 +967,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>claim count and IPC breadth - breadth is not count, label it</t>
+          <t>tls211_pat_publn.publn_claims - take it from the B1 (100% covered, mean 11.5 for granted EP), never the A1 (51%, and those are the as-filed claims). WO has 0% coverage. Breadth is not count, so label it</t>
         </is>
       </c>
     </row>
@@ -978,7 +1012,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (strong): every family member's filing authority - the actual footprint (which markets are the *relevant* ones stays judgement)</t>
+          <t>-&gt; notebook 2 (strong): designated_states at grant vs the states still paid for - tls231 lapse_country for lapses, PGFP fee_country for what is still in force (which markets are the *relevant* ones stays judgement)</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -999,7 +1033,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>every family member's filing authority - the actual footprint (which markets are the *relevant* ones stays judgement)</t>
+          <t>designated_states at grant vs the states still paid for - tls231 lapse_country for lapses, PGFP fee_country for what is still in force (which markets are the *relevant* ones stays judgement)</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1132,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (open): opposition frequency in that authority/IPC - needs legal-event tables (O1)</t>
+          <t>-&gt; notebook 2 (good): opposition frequency from tls231: the 26N/26 pair gives both halves of the fraction (EP baseline ~4.5%), and 27O/27A/27W give the outcome</t>
         </is>
       </c>
       <c r="J8" t="b">
@@ -1114,12 +1148,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>good</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>opposition frequency in that authority/IPC - needs legal-event tables (O1)</t>
+          <t>opposition frequency from tls231: the 26N/26 pair gives both halves of the fraction (EP baseline ~4.5%), and 27O/27A/27W give the outcome</t>
         </is>
       </c>
     </row>

--- a/8_ipscore_rebuild/4_tool/ipscore_valuation_data.xlsx
+++ b/8_ipscore_rebuild/4_tool/ipscore_valuation_data.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1 patent and company" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2 all forty answers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3 profile" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4 money parameters" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5 cash flow" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6 sensitivity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 patent and company" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 all forty answers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 profile" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 money parameters" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 cash flow" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 evidence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 sensitivity" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,12 +435,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -638,82 +651,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>section_title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>carries_money</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>oek_param</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>oek_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>is_risk_driver</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>is_opportunity_driver</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>patstat_strength</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>patstat_sources</t>
         </is>
@@ -746,21 +759,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Patent granted</t>
+          <t>Opposition period expired</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (strong): tls201_appln.granted ('Y'/'N') + publication kind codes, plus the opposition outcome from tls231 (26N none / 26 filed / 27W revoked)</t>
+          <t>granted, and the opposition period expired with no opposition filed (26N, effective 2018-10-11)</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -866,21 +879,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Patent has 8-12 year term remaining</t>
+          <t>Patent has 4-8 year term remaining</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>measured</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (strong): earliest filing date + 20 years for the nominal term, and tls231 PGFP renewal payments (fee_renewal_year) for how far fees are actually paid</t>
+          <t>earliest filing 2014-06-13, nominal expiry 2034-06-13 = 7.8 years left; renewals paid to year 11 in DE, FR, GB, SE</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -932,21 +945,21 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The claims are reasonably broad</t>
+          <t>The claims are broadly inclusive</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>informed</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (proxy): tls211_pat_publn.publn_claims - take it from the B1 (100% covered, mean 11.5 for granted EP), never the A1 (51%, and those are the as-filed claims). WO has 0% coverage. Breadth is not count, so label it</t>
+          <t>19 claims in the granted EP B1 vs a mean of 11.5 for granted EP - a proxy for breadth, not a measure of it</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -1007,12 +1020,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>informed</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (strong): designated_states at grant vs the states still paid for - tls231 lapse_country for lapses, PGFP fee_country for what is still in force (which markets are the *relevant* ones stays judgement)</t>
+          <t>designated in 38 EPC states at grant, lapsed in 34; in force in ['DE', 'FR', 'GB', 'SE'] plus national grants in ['AU', 'CA', 'CN', 'JP', 'KR', 'US'] = 10 territories</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -1127,12 +1140,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>informed</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (good): opposition frequency from tls231: the 26N/26 pair gives both halves of the fraction (EP baseline ~4.5%), and 27O/27A/27W give the outcome</t>
+          <t>22,141 of 330,611 granted EP patents in C12M, C12P, C12Q, G01N, G06T were opposed = 6.7% (EP baseline 4.5%) -&gt; disputes are customary</t>
         </is>
       </c>
       <c r="J8" t="b">
@@ -1252,7 +1265,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (proxy): forward citations received - attention, not uniqueness</t>
+          <t>30 citing families - citations measure attention, not uniqueness. Score left as the adviser set it</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -1318,7 +1331,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (proxy): forward citations received - attention, not technical superiority</t>
+          <t>30 citing families - says nothing about technical superiority. Score left as the adviser set it</t>
         </is>
       </c>
       <c r="J11" t="b">
@@ -1942,7 +1955,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (context): size and composition of the IPC neighbourhood - context, not an answer</t>
+          <t>2,252,525 families filed 2014-2024 in C12M, C12P, C12Q, G01N, G06T - context for how crowded the field is, not an answer</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -2618,21 +2631,21 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>To a large degree</t>
+          <t>To a very large degree</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>informed</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (good): this family's jurisdictions against the applicant's historical footprint</t>
+          <t>7 of 8 jurisdictions in this family (AU, CA, CN, EP, KR, US, WO) are ones Q-LINEA had already filed in</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -2684,21 +2697,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>To some degree</t>
+          <t>To a minor degree</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>informed</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (good): jurisdictions in this family that the applicant has never filed in before</t>
+          <t>1 of 8 jurisdictions are new for Q-LINEA (JP)</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -2975,12 +2988,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>judgement</t>
+          <t>informed</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-&gt; notebook 2 (good): share of the applicant's own families in the same IPC subclass</t>
+          <t>12 of the 19 Q-LINEA families that carry an IPC symbol (out of 25 in total) are in the same subclass (C12M, C12P, C12Q) = 63%</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -3074,22 +3087,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Maximum</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Percent</t>
         </is>
@@ -3102,13 +3115,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
         <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="3">
@@ -3190,32 +3203,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>What it asks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Answer given</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Range across the 5 answers</t>
         </is>
@@ -3476,52 +3489,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>On market</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Regained</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Efficiency</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Inv. reduction</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Costs</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Investments</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Liquidity</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Discounted EUR</t>
         </is>
@@ -3878,56 +3891,522 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>What it asks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Guessed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Record says</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Moved</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Carries money</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>NPV effect (EUR)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Patent status</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>granted, and the opposition period expired with no opposition filed (26N, effective 2018-10-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Patent term remaining</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>earliest filing 2014-06-13, nominal expiry 2034-06-13 = 7.8 years left; renewals paid to year 11 in DE, FR, GB, SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Breadth of claim</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>informed</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19 claims in the granted EP B1 vs a mean of 11.5 for granted EP - a proxy for breadth, not a measure of it</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Geographical coverage</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>informed</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>designated in 38 EPC states at grant, lapsed in 34; in force in ['DE', 'FR', 'GB', 'SE'] plus national grants in ['AU', 'CA', 'CN', 'JP', 'KR', 'US'] = 10 territories</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Legal proceedings</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>informed</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>22,141 of 330,611 granted EP patents in C12M, C12P, C12Q, G01N, G06T were opposed = 6.7% (EP baseline 4.5%) -&gt; disputes are customary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unique technology</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>judgement</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30 citing families - citations measure attention, not uniqueness. Score left as the adviser set it</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Substitute technology</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>judgement</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30 citing families - says nothing about technical superiority. Score left as the adviser set it</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Competitive/substitute products</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>judgement</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2,252,525 families filed 2014-2024 in C12M, C12P, C12Q, G01N, G06T - context for how crowded the field is, not an answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Securing existing markets</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>informed</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7 of 8 jurisdictions in this family (AU, CA, CN, EP, KR, US, WO) are ones Q-LINEA had already filed in</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Winning new markets</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>informed</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1 of 8 jurisdictions are new for Q-LINEA (JP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Part of core-technology areas</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>informed</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12 of the 19 Q-LINEA families that carry an IPC symbol (out of 25 in total) are in the same subclass (C12M, C12P, C12Q) = 63%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>What it asks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Best answer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Swing</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upside left</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Downside risk</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>One step up</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>One step down</t>
         </is>
